--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -465,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data da71aa80b69aab07 | 2026-09-27T18:41:41Z</t>
+          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100.16</v>
+        <v>100.15</v>
       </c>
       <c r="G9" t="n">
         <v>187</v>
@@ -823,7 +823,7 @@
         <v>3550.83</v>
       </c>
       <c r="K9" t="n">
-        <v>355.651</v>
+        <v>355.616</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>100.16</v>
+        <v>100.15</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>181.5</v>
       </c>
       <c r="H10" t="n">
-        <v>597</v>
+        <v>598.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3548.9</v>
+        <v>3551.63</v>
       </c>
       <c r="K10" t="n">
-        <v>355.457</v>
+        <v>355.696</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>100.16</v>
+        <v>100.15</v>
       </c>
       <c r="G11" t="n">
         <v>40.2</v>
@@ -923,7 +923,7 @@
         <v>3132.87</v>
       </c>
       <c r="K11" t="n">
-        <v>313.788</v>
+        <v>313.757</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>100.16</v>
+        <v>100.15</v>
       </c>
       <c r="G12" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="H12" t="n">
         <v>365.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3132.12</v>
+        <v>3131.91</v>
       </c>
       <c r="K12" t="n">
-        <v>313.713</v>
+        <v>313.661</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>117.5</v>
+        <v>117.49</v>
       </c>
       <c r="G14" t="n">
         <v>37.6</v>
@@ -1073,7 +1073,7 @@
         <v>3676.76</v>
       </c>
       <c r="K14" t="n">
-        <v>432.02</v>
+        <v>431.983</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>117.5</v>
+        <v>117.49</v>
       </c>
       <c r="G15" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="H15" t="n">
-        <v>597</v>
+        <v>598.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3671.18</v>
+        <v>3674.45</v>
       </c>
       <c r="K15" t="n">
-        <v>431.363</v>
+        <v>431.711</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1214,16 +1214,16 @@
         <v>11.39</v>
       </c>
       <c r="G17" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="H17" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J17" t="n">
-        <v>3060.59</v>
+        <v>3062.4</v>
       </c>
       <c r="K17" t="n">
-        <v>34.86</v>
+        <v>34.881</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>117.5</v>
+        <v>117.49</v>
       </c>
       <c r="G18" t="n">
         <v>4.95</v>
       </c>
       <c r="H18" t="n">
-        <v>308.8</v>
+        <v>309.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3082.9</v>
+        <v>3083.72</v>
       </c>
       <c r="K18" t="n">
-        <v>362.24</v>
+        <v>362.307</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>128.89</v>
+        <v>128.88</v>
       </c>
       <c r="G19" t="n">
         <v>0.0344</v>
@@ -1320,13 +1320,13 @@
         <v>26.4</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9226379631096125</v>
+        <v>0.9228840227057775</v>
       </c>
       <c r="J19" t="n">
-        <v>2360.4</v>
+        <v>2361</v>
       </c>
       <c r="K19" t="n">
-        <v>304.232</v>
+        <v>304.286</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>128.89</v>
+        <v>128.88</v>
       </c>
       <c r="G20" t="n">
         <v>0.0344</v>
@@ -1376,7 +1376,7 @@
         <v>110.28</v>
       </c>
       <c r="K20" t="n">
-        <v>14.213</v>
+        <v>14.212</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>128.89</v>
+        <v>128.88</v>
       </c>
       <c r="G21" t="n">
         <v>16</v>
@@ -1426,7 +1426,7 @@
         <v>112.58</v>
       </c>
       <c r="K21" t="n">
-        <v>14.511</v>
+        <v>14.51</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>141.37</v>
+        <v>141.36</v>
       </c>
       <c r="G23" t="n">
         <v>15.5</v>
@@ -1526,7 +1526,7 @@
         <v>130.91</v>
       </c>
       <c r="K23" t="n">
-        <v>18.507</v>
+        <v>18.506</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>129.98</v>
+        <v>129.97</v>
       </c>
       <c r="G24" t="n">
         <v>5.9</v>
@@ -1576,7 +1576,7 @@
         <v>667.3200000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>86.738</v>
+        <v>86.732</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100.16</v>
+        <v>100.15</v>
       </c>
       <c r="G25" t="n">
         <v>209</v>
@@ -1626,7 +1626,7 @@
         <v>695.39</v>
       </c>
       <c r="K25" t="n">
-        <v>69.651</v>
+        <v>69.64400000000001</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10179.1</v>
+        <v>10181.4</v>
       </c>
       <c r="G28" t="n">
         <v>2.5</v>
@@ -1776,7 +1776,7 @@
         <v>65.11</v>
       </c>
       <c r="K28" t="n">
-        <v>662.765</v>
+        <v>662.915</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10179.1</v>
+        <v>10181.4</v>
       </c>
       <c r="G29" t="n">
         <v>1.7</v>
@@ -1826,7 +1826,7 @@
         <v>93.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>952.725</v>
+        <v>952.9400000000001</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0001</t>
+          <t>source:SRC-IECE-0001</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data da71aa80b69aab07 | 2026-09-27T18:41:41Z</t>
+          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
         </is>
       </c>
     </row>
@@ -1973,22 +1973,22 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>129.98</v>
+        <v>129.97</v>
       </c>
       <c r="D5" t="n">
-        <v>129.98</v>
+        <v>129.97</v>
       </c>
       <c r="E5" t="n">
-        <v>86.738</v>
+        <v>86.732</v>
       </c>
       <c r="F5" t="n">
-        <v>89.724</v>
+        <v>89.717</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.986</v>
+        <v>-2.985</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2005,16 +2005,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>128.89</v>
+        <v>128.88</v>
       </c>
       <c r="D6" t="n">
-        <v>128.89</v>
+        <v>128.88</v>
       </c>
       <c r="E6" t="n">
-        <v>14.213</v>
+        <v>14.212</v>
       </c>
       <c r="F6" t="n">
-        <v>14.511</v>
+        <v>14.51</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2037,16 +2037,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>141.37</v>
+        <v>141.36</v>
       </c>
       <c r="D7" t="n">
-        <v>141.37</v>
+        <v>141.36</v>
       </c>
       <c r="E7" t="n">
-        <v>18.472</v>
+        <v>18.471</v>
       </c>
       <c r="F7" t="n">
-        <v>18.507</v>
+        <v>18.506</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>10307.99</v>
+        <v>10310.28</v>
       </c>
       <c r="D8" t="n">
-        <v>10307.99</v>
+        <v>10310.28</v>
       </c>
       <c r="E8" t="n">
-        <v>966.997</v>
+        <v>967.201</v>
       </c>
       <c r="F8" t="n">
-        <v>966.938</v>
+        <v>967.153</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.059</v>
+        <v>0.048</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2201,22 +2201,22 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1168.19</v>
+        <v>1168.16</v>
       </c>
       <c r="D12" t="n">
-        <v>1168.19</v>
+        <v>1168.16</v>
       </c>
       <c r="E12" t="n">
-        <v>971.572</v>
+        <v>971.511</v>
       </c>
       <c r="F12" t="n">
-        <v>969.534</v>
+        <v>969.455</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.038</v>
+        <v>2.057</v>
       </c>
       <c r="I12" t="n">
         <v>2.011</v>
@@ -2237,13 +2237,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10179.1</v>
+        <v>10181.4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>952.725</v>
+        <v>952.9400000000001</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>952.725</v>
+        <v>952.9400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2269,22 +2269,22 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>329.21</v>
+        <v>329.18</v>
       </c>
       <c r="D14" t="n">
-        <v>329.21</v>
+        <v>329.18</v>
       </c>
       <c r="E14" t="n">
-        <v>1136.353</v>
+        <v>1136.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1135.394</v>
+        <v>1135.948</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.959</v>
+        <v>0.301</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2304,19 +2304,19 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10179.1</v>
+        <v>10181.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>662.765</v>
+        <v>662.915</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-662.765</v>
+        <v>-662.915</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2333,22 +2333,22 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>229.05</v>
+        <v>229.03</v>
       </c>
       <c r="D16" t="n">
-        <v>229.05</v>
+        <v>229.03</v>
       </c>
       <c r="E16" t="n">
-        <v>821.681</v>
+        <v>822.288</v>
       </c>
       <c r="F16" t="n">
-        <v>618.02</v>
+        <v>618.043</v>
       </c>
       <c r="G16" t="n">
-        <v>203.659</v>
+        <v>204.249</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2426,7 +2426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data da71aa80b69aab07 | 2026-09-27T18:41:41Z</t>
+          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3094</v>
+        <v>3093.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>enthalpy rise 2,986 kW / motor 0.965</t>
+          <t>enthalpy rise 2,985 kW / motor 0.965</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1935.2</v>
+        <v>1935.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10,179 kg/s x g x 16.0 m / (0.86 x 0.96)</t>
+          <t>10,181 kg/s x g x 16.0 m / (0.86 x 0.96)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data da71aa80b69aab07 | 2026-09-27T18:41:41Z</t>
+          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200.31</v>
+        <v>200.89</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>625.3099999999999</v>
+        <v>625.89</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.31723459615531</v>
+        <v>10.31735666674105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>613.0627654038447</v>
+        <v>613.6426433332589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5650.12225622523</v>
+        <v>5644.886398632664</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5762.995483362692</v>
+        <v>5757.549587572328</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.46751381972992</v>
+        <v>62.52659999265313</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.95858607669081</v>
+        <v>1.956790596868627</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36049.22677369851</v>
+        <v>36057.37221107307</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data da71aa80b69aab07 | 2026-09-27T18:41:41Z</t>
+          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>energy balance COND: residual +0.059 MW (tolerance 0.97 MW)</t>
+          <t>energy balance COND: residual +0.048 MW (tolerance 0.97 MW)</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>energy balance HRSG: residual +2.038 MW vs stated casing loss 2.011 MW (tolerance 0.97 MW)</t>
+          <t>energy balance HRSG: residual +2.057 MW vs stated casing loss 2.011 MW (tolerance 0.97 MW)</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>energy balance PIPE: residual +0.959 MW (tolerance 1.14 MW)</t>
+          <t>energy balance PIPE: residual +0.301 MW (tolerance 1.14 MW)</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>energy balance ST: residual +0.001 MW (tolerance 0.82 MW)</t>
+          <t>energy balance ST: residual -0.004 MW (tolerance 0.82 MW)</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>net export 613.1 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>net export 613.6 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gross output 625.31 MW vs IG-01 &gt;= 614.00 (margin +1.84 %)</t>
+          <t>gross output 625.89 MW vs IG-01 &gt;= 615.00 (margin +1.77 %)</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gross heat rate 5,650.12 kJ/kWh vs IG-02 &lt;= 5,745.00 (margin +1.65 %)</t>
+          <t>gross heat rate 5,644.89 kJ/kWh vs IG-02 &lt;= 5,735.00 (margin +1.57 %)</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>net output 613.06 MW vs PG-01 &gt;= 600.00 (margin +2.18 %)</t>
+          <t>net output 613.64 MW vs PG-01 &gt;= 600.00 (margin +2.27 %)</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>net heat rate 5,763.00 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.66 %)</t>
+          <t>net heat rate 5,757.55 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.75 %)</t>
         </is>
       </c>
     </row>
@@ -4150,14 +4150,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 601.8 MW / 5,862 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
+          <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 602.8 MW / 5,852 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -465,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
+          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
         </is>
       </c>
     </row>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>776.01</v>
+        <v>776.006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.01</v>
+        <v>1.012</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fuel gas at performance gas heater inlet (IEC terminal point)</t>
+          <t>Fuel gas at performance gas heater inlet (IEC terminal point IF-01)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20.67</v>
+        <v>20.672</v>
       </c>
       <c r="G5" t="n">
         <v>38</v>
@@ -632,7 +632,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20.67</v>
+        <v>20.672</v>
       </c>
       <c r="G6" t="n">
         <v>35.5</v>
@@ -673,7 +673,7 @@
         <v>457.77</v>
       </c>
       <c r="K6" t="n">
-        <v>9.462</v>
+        <v>9.462999999999999</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>796.6799999999999</v>
+        <v>796.678</v>
       </c>
       <c r="G7" t="n">
-        <v>1.05</v>
+        <v>1.048</v>
       </c>
       <c r="H7" t="n">
         <v>640</v>
@@ -723,7 +723,7 @@
         <v>689.9</v>
       </c>
       <c r="K7" t="n">
-        <v>549.627</v>
+        <v>549.629</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>796.6799999999999</v>
+        <v>796.678</v>
       </c>
       <c r="G8" t="n">
-        <v>1.01</v>
+        <v>1.014</v>
       </c>
       <c r="H8" t="n">
-        <v>80.5</v>
+        <v>80.16</v>
       </c>
       <c r="J8" t="n">
-        <v>58.75</v>
+        <v>58.38</v>
       </c>
       <c r="K8" t="n">
-        <v>46.802</v>
+        <v>46.514</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100.15</v>
+        <v>100.155</v>
       </c>
       <c r="G9" t="n">
         <v>187</v>
@@ -823,7 +823,7 @@
         <v>3550.83</v>
       </c>
       <c r="K9" t="n">
-        <v>355.616</v>
+        <v>355.634</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>100.15</v>
+        <v>100.155</v>
       </c>
       <c r="G10" t="n">
         <v>181.5</v>
@@ -873,7 +873,7 @@
         <v>3551.63</v>
       </c>
       <c r="K10" t="n">
-        <v>355.696</v>
+        <v>355.714</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -911,19 +911,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>100.15</v>
+        <v>100.155</v>
       </c>
       <c r="G11" t="n">
         <v>40.2</v>
       </c>
       <c r="H11" t="n">
-        <v>366.2</v>
+        <v>366.21</v>
       </c>
       <c r="J11" t="n">
-        <v>3132.87</v>
+        <v>3132.89</v>
       </c>
       <c r="K11" t="n">
-        <v>313.757</v>
+        <v>313.775</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>100.15</v>
+        <v>100.155</v>
       </c>
       <c r="G12" t="n">
         <v>39.5</v>
       </c>
       <c r="H12" t="n">
-        <v>365.2</v>
+        <v>365.21</v>
       </c>
       <c r="J12" t="n">
-        <v>3131.91</v>
+        <v>3131.93</v>
       </c>
       <c r="K12" t="n">
-        <v>313.661</v>
+        <v>313.679</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>17.34</v>
+        <v>17.338</v>
       </c>
       <c r="G13" t="n">
         <v>40.3</v>
@@ -1023,7 +1023,7 @@
         <v>3041.69</v>
       </c>
       <c r="K13" t="n">
-        <v>52.743</v>
+        <v>52.737</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>117.49</v>
+        <v>117.493</v>
       </c>
       <c r="G14" t="n">
         <v>37.6</v>
@@ -1073,7 +1073,7 @@
         <v>3676.76</v>
       </c>
       <c r="K14" t="n">
-        <v>431.983</v>
+        <v>431.994</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>117.49</v>
+        <v>117.493</v>
       </c>
       <c r="G15" t="n">
         <v>36.2</v>
@@ -1123,7 +1123,7 @@
         <v>3674.45</v>
       </c>
       <c r="K15" t="n">
-        <v>431.711</v>
+        <v>431.722</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11.39</v>
+        <v>11.901</v>
       </c>
       <c r="G16" t="n">
         <v>5.4</v>
       </c>
       <c r="H16" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="J16" t="n">
-        <v>3063.58</v>
+        <v>2959.75</v>
       </c>
       <c r="K16" t="n">
-        <v>34.894</v>
+        <v>35.224</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1211,19 +1211,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11.39</v>
+        <v>11.901</v>
       </c>
       <c r="G17" t="n">
         <v>5.05</v>
       </c>
       <c r="H17" t="n">
-        <v>299</v>
+        <v>249</v>
       </c>
       <c r="J17" t="n">
-        <v>3062.4</v>
+        <v>2958.88</v>
       </c>
       <c r="K17" t="n">
-        <v>34.881</v>
+        <v>35.214</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>117.49</v>
+        <v>117.493</v>
       </c>
       <c r="G18" t="n">
         <v>4.95</v>
@@ -1273,7 +1273,7 @@
         <v>3083.72</v>
       </c>
       <c r="K18" t="n">
-        <v>362.307</v>
+        <v>362.316</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>128.88</v>
+        <v>129.394</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0344</v>
+        <v>0.03444</v>
       </c>
       <c r="H19" t="n">
         <v>26.4</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9228840227057775</v>
+        <v>0.920612334240572</v>
       </c>
       <c r="J19" t="n">
-        <v>2361</v>
+        <v>2355.5</v>
       </c>
       <c r="K19" t="n">
-        <v>304.286</v>
+        <v>304.788</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1364,19 +1364,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>128.88</v>
+        <v>129.394</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0344</v>
+        <v>0.03444</v>
       </c>
       <c r="H20" t="n">
-        <v>26.3</v>
+        <v>26.35</v>
       </c>
       <c r="J20" t="n">
-        <v>110.28</v>
+        <v>110.48</v>
       </c>
       <c r="K20" t="n">
-        <v>14.212</v>
+        <v>14.296</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1414,19 +1414,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>128.88</v>
+        <v>129.394</v>
       </c>
       <c r="G21" t="n">
         <v>16</v>
       </c>
       <c r="H21" t="n">
-        <v>26.5</v>
+        <v>26.52</v>
       </c>
       <c r="J21" t="n">
-        <v>112.58</v>
+        <v>112.67</v>
       </c>
       <c r="K21" t="n">
-        <v>14.51</v>
+        <v>14.578</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12.48</v>
+        <v>12.481</v>
       </c>
       <c r="G22" t="n">
         <v>43</v>
@@ -1476,7 +1476,7 @@
         <v>317.41</v>
       </c>
       <c r="K22" t="n">
-        <v>3.961</v>
+        <v>3.962</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>141.36</v>
+        <v>141.874</v>
       </c>
       <c r="G23" t="n">
         <v>15.5</v>
       </c>
       <c r="H23" t="n">
-        <v>30.9</v>
+        <v>30.85</v>
       </c>
       <c r="J23" t="n">
-        <v>130.91</v>
+        <v>130.7</v>
       </c>
       <c r="K23" t="n">
-        <v>18.506</v>
+        <v>18.544</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>129.97</v>
+        <v>129.973</v>
       </c>
       <c r="G24" t="n">
         <v>5.9</v>
       </c>
       <c r="H24" t="n">
-        <v>158.1</v>
+        <v>158.13</v>
       </c>
       <c r="J24" t="n">
-        <v>667.3200000000001</v>
+        <v>667.45</v>
       </c>
       <c r="K24" t="n">
-        <v>86.732</v>
+        <v>86.751</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HP feedwater at BFP discharge</t>
+          <t>HP feedwater at BFP discharge to HP economiser</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100.15</v>
+        <v>100.155</v>
       </c>
       <c r="G25" t="n">
         <v>209</v>
       </c>
       <c r="H25" t="n">
-        <v>161.8</v>
+        <v>161.83</v>
       </c>
       <c r="J25" t="n">
-        <v>695.39</v>
+        <v>695.52</v>
       </c>
       <c r="K25" t="n">
-        <v>69.64400000000001</v>
+        <v>69.66</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IP feedwater at BFP interstage outlet</t>
+          <t>IP feedwater at BFP interstage to IP economiser</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>29.82</v>
+        <v>29.819</v>
       </c>
       <c r="G26" t="n">
         <v>46</v>
       </c>
       <c r="H26" t="n">
-        <v>158.9</v>
+        <v>158.89</v>
       </c>
       <c r="J26" t="n">
-        <v>673.15</v>
+        <v>673.11</v>
       </c>
       <c r="K26" t="n">
-        <v>20.073</v>
+        <v>20.071</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12.48</v>
+        <v>12.481</v>
       </c>
       <c r="G27" t="n">
         <v>43.3</v>
       </c>
       <c r="H27" t="n">
-        <v>248</v>
+        <v>247.98</v>
       </c>
       <c r="J27" t="n">
-        <v>1075.98</v>
+        <v>1075.88</v>
       </c>
       <c r="K27" t="n">
         <v>13.428</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10181.4</v>
+        <v>10196.804</v>
       </c>
       <c r="G28" t="n">
         <v>2.5</v>
@@ -1776,7 +1776,7 @@
         <v>65.11</v>
       </c>
       <c r="K28" t="n">
-        <v>662.915</v>
+        <v>663.918</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10181.4</v>
+        <v>10196.804</v>
       </c>
       <c r="G29" t="n">
         <v>1.7</v>
@@ -1826,7 +1826,7 @@
         <v>93.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>952.9400000000001</v>
+        <v>954.3819999999999</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>source:SRC-IECE-0001</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
+          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>776.01</v>
+        <v>776.006</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1973,22 +1973,22 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>129.97</v>
+        <v>129.973</v>
       </c>
       <c r="D5" t="n">
-        <v>129.97</v>
+        <v>129.974</v>
       </c>
       <c r="E5" t="n">
-        <v>86.732</v>
+        <v>86.751</v>
       </c>
       <c r="F5" t="n">
-        <v>89.717</v>
+        <v>89.732</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.985</v>
+        <v>-2.981</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2005,22 +2005,22 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>128.88</v>
+        <v>129.394</v>
       </c>
       <c r="D6" t="n">
-        <v>128.88</v>
+        <v>129.394</v>
       </c>
       <c r="E6" t="n">
-        <v>14.212</v>
+        <v>14.296</v>
       </c>
       <c r="F6" t="n">
-        <v>14.51</v>
+        <v>14.578</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.297</v>
+        <v>-0.282</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -2037,22 +2037,22 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>141.36</v>
+        <v>141.875</v>
       </c>
       <c r="D7" t="n">
-        <v>141.36</v>
+        <v>141.874</v>
       </c>
       <c r="E7" t="n">
-        <v>18.471</v>
+        <v>18.54</v>
       </c>
       <c r="F7" t="n">
-        <v>18.506</v>
+        <v>18.544</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.035</v>
+        <v>-0.004</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>10310.28</v>
+        <v>10326.198</v>
       </c>
       <c r="D8" t="n">
-        <v>10310.28</v>
+        <v>10326.198</v>
       </c>
       <c r="E8" t="n">
-        <v>967.201</v>
+        <v>968.706</v>
       </c>
       <c r="F8" t="n">
-        <v>967.153</v>
+        <v>968.678</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.048</v>
+        <v>0.027</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2101,22 +2101,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>33.15</v>
+        <v>33.153</v>
       </c>
       <c r="D9" t="n">
-        <v>33.15</v>
+        <v>33.153</v>
       </c>
       <c r="E9" t="n">
         <v>13.428</v>
       </c>
       <c r="F9" t="n">
-        <v>13.423</v>
+        <v>13.425</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>20.67</v>
+        <v>20.672</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2165,22 +2165,22 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>796.6799999999999</v>
+        <v>796.678</v>
       </c>
       <c r="D11" t="n">
-        <v>796.6799999999999</v>
+        <v>796.678</v>
       </c>
       <c r="E11" t="n">
-        <v>983.042</v>
+        <v>983.138</v>
       </c>
       <c r="F11" t="n">
-        <v>549.627</v>
+        <v>549.629</v>
       </c>
       <c r="G11" t="n">
         <v>433.527</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.113</v>
+        <v>-0.018</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2201,29 +2201,29 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1168.16</v>
+        <v>1168.681</v>
       </c>
       <c r="D12" t="n">
-        <v>1168.16</v>
+        <v>1168.681</v>
       </c>
       <c r="E12" t="n">
-        <v>971.511</v>
+        <v>971.583</v>
       </c>
       <c r="F12" t="n">
-        <v>969.455</v>
+        <v>969.544</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.057</v>
+        <v>2.039</v>
       </c>
       <c r="I12" t="n">
-        <v>2.011</v>
+        <v>2.012</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HRSG: gas-side duty 502.83 MW; residual = casing loss</t>
+          <t>HRSG: gas-side duty 503.12 MW; residual = casing loss</t>
         </is>
       </c>
     </row>
@@ -2237,13 +2237,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10181.4</v>
+        <v>10196.804</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>952.9400000000001</v>
+        <v>954.3819999999999</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>952.9400000000001</v>
+        <v>954.3819999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2269,22 +2269,22 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>329.18</v>
+        <v>329.704</v>
       </c>
       <c r="D14" t="n">
-        <v>329.18</v>
+        <v>329.704</v>
       </c>
       <c r="E14" t="n">
-        <v>1136.25</v>
+        <v>1136.626</v>
       </c>
       <c r="F14" t="n">
-        <v>1135.948</v>
+        <v>1136.328</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.301</v>
+        <v>0.298</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2304,19 +2304,19 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10181.4</v>
+        <v>10196.804</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>662.915</v>
+        <v>663.918</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-662.915</v>
+        <v>-663.918</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2333,22 +2333,22 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>229.03</v>
+        <v>229.549</v>
       </c>
       <c r="D16" t="n">
-        <v>229.03</v>
+        <v>229.549</v>
       </c>
       <c r="E16" t="n">
-        <v>822.288</v>
+        <v>822.649</v>
       </c>
       <c r="F16" t="n">
-        <v>618.043</v>
+        <v>618.563</v>
       </c>
       <c r="G16" t="n">
-        <v>204.249</v>
+        <v>204.086</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2369,13 +2369,13 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>796.6799999999999</v>
+        <v>796.678</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>46.802</v>
+        <v>46.514</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>46.802</v>
+        <v>46.514</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2426,7 +2426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
+          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GT GSU losses at SRC load</t>
+          <t>GT GSU losses at this case load</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0007</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ST GSU losses at SRC load</t>
+          <t>ST GSU losses at this case load</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>source:SRC-EPCE-0007</t>
+          <t>source:SRC-IECE-0005</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3093.7</v>
+        <v>3089</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>enthalpy rise 2,985 kW / motor 0.965</t>
+          <t>enthalpy rise 2,981 kW / motor 0.965</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>313</v>
+        <v>297.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>enthalpy rise 297 kW / motor 0.95</t>
+          <t>enthalpy rise 282 kW / motor 0.95</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1935.6</v>
+        <v>1938.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10,181 kg/s x g x 16.0 m / (0.86 x 0.96)</t>
+          <t>10,197 kg/s x g x 16.0 m / (0.86 x 0.96)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
+          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200.89</v>
+        <v>200.73</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>625.89</v>
+        <v>625.73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.31735666674105</v>
+        <v>10.29973770756298</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.93</v>
+        <v>1.931</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>613.6426433332589</v>
+        <v>613.499262292437</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>981.4105411222773</v>
+        <v>981.5055010198217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5644.886398632664</v>
+        <v>5646.876134549019</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5757.549587572328</v>
+        <v>5759.45240825258</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.52659999265313</v>
+        <v>62.50594231565568</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.956790596868627</v>
+        <v>1.954635019507292</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.67</v>
+        <v>20.672</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>101584.4734607791</v>
+        <v>101594.3026309253</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>502.825727623546</v>
+        <v>503.1151361035818</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36057.37221107307</v>
+        <v>36111.92539251564</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34.4</v>
+        <v>34.44</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.471</v>
+        <v>4.472</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.673</v>
+        <v>9.673999999999999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>73.855</v>
+        <v>73.854</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.118</v>
+        <v>11.117</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.0.0 | data 745a1d896d59ed4c | 2026-09-27T18:48:55Z</t>
+          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>energy balance CMIX: residual -0.035 MW (tolerance 0.25 MW)</t>
+          <t>energy balance CMIX: residual -0.004 MW (tolerance 0.25 MW)</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>energy balance COND: residual +0.048 MW (tolerance 0.97 MW)</t>
+          <t>energy balance COND: residual +0.027 MW (tolerance 0.97 MW)</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>energy balance FGH: residual +0.005 MW (tolerance 0.25 MW)</t>
+          <t>energy balance FGH: residual +0.003 MW (tolerance 0.25 MW)</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>energy balance GT: residual -0.113 MW (tolerance 0.98 MW)</t>
+          <t>energy balance GT: residual -0.018 MW (tolerance 0.98 MW)</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>energy balance HRSG: residual +2.057 MW vs stated casing loss 2.011 MW (tolerance 0.97 MW)</t>
+          <t>energy balance HRSG: residual +2.039 MW vs stated casing loss 2.012 MW (tolerance 0.97 MW)</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>energy balance PIPE: residual +0.301 MW (tolerance 1.14 MW)</t>
+          <t>energy balance PIPE: residual +0.298 MW (tolerance 1.14 MW)</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>energy balance ST: residual -0.004 MW (tolerance 0.82 MW)</t>
+          <t>energy balance ST: residual +0.000 MW (tolerance 0.82 MW)</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>auxiliary + transformer losses 1.96 % of gross vs DP-CASE-0031 &lt;= 2.2 %</t>
+          <t>auxiliary + transformer losses 1.95 % of gross vs DP-CASE-0031 &lt;= 2.2 %</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>condenser pressure 34.40 mbar(a) vs DP-OWNR-0021 &lt;= 36.0 mbar(a)</t>
+          <t>condenser pressure 34.44 mbar(a) vs DP-OWNR-0021 &lt;= 36.0 mbar(a)</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gas flow 101,584 Sm3/h = 88.3 % of DP-OWNR-0033 (115,000 Sm3/h)</t>
+          <t>gas flow 101,594 Sm3/h = 88.3 % of DP-OWNR-0033 (115,000 Sm3/h)</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>net export 613.6 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>net export 613.5 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gross output 625.89 MW vs IG-01 &gt;= 615.00 (margin +1.77 %)</t>
+          <t>gross output 625.73 MW vs IG-01 &gt;= 615.00 (margin +1.74 %)</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gross heat rate 5,644.89 kJ/kWh vs IG-02 &lt;= 5,735.00 (margin +1.57 %)</t>
+          <t>gross heat rate 5,646.88 kJ/kWh vs IG-02 &lt;= 5,735.00 (margin +1.54 %)</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>condenser pressure 34.40 mbar(a) vs IG-04 &lt;= 35.50 (margin +3.10 %)</t>
+          <t>condenser pressure 34.44 mbar(a) vs IG-04 &lt;= 35.50 (margin +2.99 %)</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>net output 613.64 MW vs PG-01 &gt;= 600.00 (margin +2.27 %)</t>
+          <t>net output 613.50 MW vs PG-01 &gt;= 600.00 (margin +2.25 %)</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>net heat rate 5,757.55 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.75 %)</t>
+          <t>net heat rate 5,759.45 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.72 %)</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 602.8 MW / 5,852 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
+          <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 602.8 MW / 5,851 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,10 +36,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,11 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -4006,14 +4001,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fuel LHV from the composition (ISO 6976) 47.48 MJ/kg vs DP-CASE-0018 48.4 MJ/kg (-1.90 %)</t>
+          <t>fuel LHV from the composition (ISO 6976) 47.48 MJ/kg vs DP-CASE-0018 47.48 MJ/kg (-0.00 %)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.29973770756298</v>
+        <v>9.859737707562982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>613.499262292437</v>
+        <v>613.939262292437</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5759.45240825258</v>
+        <v>5755.324705049224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.50594231565568</v>
+        <v>62.55077140724434</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.954635019507292</v>
+        <v>1.884317150777968</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>auxiliary + transformer losses 1.95 % of gross vs DP-CASE-0031 &lt;= 2.2 %</t>
+          <t>auxiliary + transformer losses 1.88 % of gross vs DP-CASE-0031 &lt;= 2.2 %</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gas flow 101,594 Sm3/h = 88.3 % of DP-OWNR-0033 (115,000 Sm3/h)</t>
+          <t>gas flow 101,594 Sm3/h = 84.7 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>net export 613.5 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>net export 613.9 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>net output 613.50 MW vs PG-01 &gt;= 600.00 (margin +2.25 %)</t>
+          <t>net output 613.94 MW vs PG-01 &gt;= 600.00 (margin +2.32 %)</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>net heat rate 5,759.45 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.72 %)</t>
+          <t>net heat rate 5,755.32 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.79 %)</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 602.8 MW / 5,851 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
+          <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 603.2 MW / 5,847 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -1831,6 +1831,56 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>source:SRC-IECE-0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fuel gas to the station preheater burners (water-bath heaters)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fuel_gas</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FGS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PHB</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-21.08</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>preliminary</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>decision:DEC-EPCE-0014</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1870,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -2131,19 +2181,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>20.672</v>
+        <v>20.704</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2257,29 +2307,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>PHB</t>
         </is>
       </c>
       <c r="B14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>329.704</v>
+        <v>0.032</v>
       </c>
       <c r="D14" t="n">
-        <v>329.704</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1136.626</v>
+        <v>-0.001</v>
       </c>
       <c r="F14" t="n">
-        <v>1136.328</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.298</v>
+        <v>-0.001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2289,29 +2339,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="B15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>329.704</v>
       </c>
       <c r="D15" t="n">
-        <v>10196.804</v>
+        <v>329.704</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1136.626</v>
       </c>
       <c r="F15" t="n">
-        <v>663.918</v>
+        <v>1136.328</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-663.918</v>
+        <v>0.298</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2321,70 +2371,102 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>229.549</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>229.549</v>
+        <v>10196.804</v>
       </c>
       <c r="E16" t="n">
-        <v>822.649</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>618.563</v>
+        <v>663.918</v>
       </c>
       <c r="G16" t="n">
-        <v>204.086</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-663.918</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>229.549</v>
+      </c>
+      <c r="D17" t="n">
+        <v>229.549</v>
+      </c>
+      <c r="E17" t="n">
+        <v>822.649</v>
+      </c>
+      <c r="F17" t="n">
+        <v>618.563</v>
+      </c>
+      <c r="G17" t="n">
+        <v>204.086</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="B17" t="b">
+      <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>796.678</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>46.514</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>46.514</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2421,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3691,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>981.5055010198217</v>
+        <v>983.0248593805336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3639,7 +3721,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5755.324705049224</v>
+        <v>5764.233876419269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3654,7 +3736,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.55077140724434</v>
+        <v>62.45409324432742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3714,7 +3796,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.672</v>
+        <v>20.704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3729,7 +3811,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>101594.3026309253</v>
+        <v>101751.5693532642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3900,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4126,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gas flow 101,594 Sm3/h = 84.7 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
+          <t>gas flow 101,752 Sm3/h = 84.8 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4210,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>net heat rate 5,755.32 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.79 %)</t>
+          <t>net heat rate 5,764.23 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.63 %)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-100.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-100.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3982,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fuel LHV from the composition (ISO 6976) 47.48 MJ/kg vs DP-CASE-0018 47.48 MJ/kg (-0.00 %)</t>
+          <t>CW temperature rise 7.00 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>auxiliary + transformer losses 1.88 % of gross vs DP-CASE-0031 &lt;= 2.2 %</t>
+          <t>fuel LHV from the composition (ISO 6976) 47.48 MJ/kg vs DP-CASE-0018 47.48 MJ/kg (-0.00 %)</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>condenser pressure 34.44 mbar(a) vs DP-OWNR-0021 &lt;= 36.0 mbar(a)</t>
+          <t>auxiliary + transformer losses 1.88 % of gross vs DP-CASE-0031 &lt;= 2.2 %</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gas flow 101,752 Sm3/h = 84.8 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
+          <t>condenser pressure 34.44 mbar(a) vs DP-OWNR-0021 &lt;= 36.0 mbar(a)</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>net export 613.9 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
+          <t>gas flow 101,752 Sm3/h = 84.8 % of DP-OWNR-0033 (120,000 Sm3/h)</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gross output 625.73 MW vs IG-01 &gt;= 615.00 (margin +1.74 %)</t>
+          <t>net export 613.9 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gross heat rate 5,646.88 kJ/kWh vs IG-02 &lt;= 5,735.00 (margin +1.54 %)</t>
+          <t>gross output 625.73 MW vs IG-01 &gt;= 615.00 (margin +1.74 %)</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GT output 425.00 MW vs IG-03 &gt;= 418.00 (margin +1.67 %)</t>
+          <t>gross heat rate 5,646.88 kJ/kWh vs IG-02 &lt;= 5,735.00 (margin +1.54 %)</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>condenser pressure 34.44 mbar(a) vs IG-04 &lt;= 35.50 (margin +2.99 %)</t>
+          <t>GT output 425.00 MW vs IG-03 &gt;= 418.00 (margin +1.67 %)</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>net output 613.94 MW vs PG-01 &gt;= 600.00 (margin +2.32 %)</t>
+          <t>condenser pressure 34.44 mbar(a) vs IG-04 &lt;= 35.50 (margin +2.99 %)</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>net heat rate 5,764.23 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.63 %)</t>
+          <t>net output 613.94 MW vs PG-01 &gt;= 600.00 (margin +2.32 %)</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CW temperature rise 7.00 K vs PG-13 &lt;= 7.00 (margin +0.00 %)</t>
+          <t>net heat rate 5,764.23 kJ/kWh vs PG-02 &lt;= 5,860.00 (margin +1.63 %)</t>
         </is>
       </c>
     </row>
@@ -4233,6 +4233,18 @@
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>CW temperature rise 7.00 K vs PG-13 &lt;= 7.00 (margin +0.00 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>guarantee cover: at IG-01/IG-02 limits and this HMB's auxiliaries the net plant is 603.2 MW / 5,847 kJ/kWh vs Owner PG-01 600 MW / PG-02 5,860 kJ/kWh</t>
         </is>
